--- a/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_iteration_1.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_2_['No. 91_～ば〈条件(じょうけん)〉 ']_revised_iteration_1.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 お金があれば、(   )。</t>
+          <t>: もんだい1 お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 時間があれば、(   )。</t>
+          <t>: もんだい1 時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 この道をまっすぐ行けば、(   )。</t>
+          <t>: もんだい1 この道をまっすぐ行けば、(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 いい天気ならば、(   )。</t>
+          <t>: もんだい1 いい天気ならば、(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 彼が来れば、(   )。</t>
+          <t>: もんだい1 彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 安ければ、(   )。</t>
+          <t>: もんだい1 安ければ、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 早く起きれば、(   )。</t>
+          <t>: もんだい1 早く起きれば、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 日本語が上手になれば、(   )。</t>
+          <t>: もんだい1 日本語が上手になれば、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 勉強すれば、(   )。</t>
+          <t>: もんだい1 勉強すれば、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨が 降れば 試合は 中止に (   )。</t>
+          <t>: もんだい2 雨が降れば、試合は(   )。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. なる 2. する 3. いる 4. ある</t>
+          <t>1. 中止になる 2. 中止する 3. 中止で 4. 中止だ</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -702,12 +702,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あれば 本を (   )。</t>
+          <t>: もんだい2 時間が あれば 本を (   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -726,12 +726,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金を ためれば 新しい パソコンを (   )。</t>
+          <t>: もんだい2 お金を ためれば 新しい パソコンを (   )。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -750,12 +750,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 早く 寝れば 朝 元気に (   )。</t>
+          <t>: もんだい2 早く 寝れば 朝 元気に (   )。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -774,12 +774,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 仕事が 終われば 友達と (   )。</t>
+          <t>: もんだい2 仕事が 終われば 友達と (   )。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 天気が 良ければ ピクニックに (   )。</t>
+          <t>: もんだい2 天気が 良ければ ピクニックに (   )。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -822,12 +822,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 暇が あれば 映画を (   )。</t>
+          <t>: もんだい2 暇が あれば 映画を (   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -846,12 +846,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が あれば、手伝いに (   )。</t>
+          <t>: もんだい2 時間が あれば、手伝いに (   )。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 勉強すれば、試験に (   )。</t>
+          <t>: もんだい2 勉強すれば、試験に (   )。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -894,12 +894,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金が あれば、旅行に (   )。</t>
+          <t>: もんだい2 お金が あれば、旅行に (   )。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -918,22 +918,22 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降れば、試合は(   )。</t>
+          <t>: もんだい3 雨が降れば、試合は(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. 中止だ 2. 中止にする 3. 中止で 4. 中止になる</t>
+          <t>1. 中止です 2. 中止にします 3. 中止になります 4. 中止できます</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr"/>
@@ -942,12 +942,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 この薬を飲めば、すぐに(   )。</t>
+          <t>: もんだい3 この薬を飲めば、すぐに(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -966,12 +966,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があれば、映画を(   )。</t>
+          <t>: もんだい3 時間があれば、映画を(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金があれば、あの車を(   )。</t>
+          <t>: もんだい3 お金があれば、あの車を(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達が来れば、パーティーがもっと(   )。</t>
+          <t>: もんだい3 友達が来れば、パーティーがもっと(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1038,12 +1038,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 天気が良ければ、ピクニックに(   )。</t>
+          <t>: もんだい3 天気が良ければ、ピクニックに(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1062,12 +1062,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 もっと勉強すれば、試験に(   )。</t>
+          <t>: もんだい3 もっと勉強すれば、試験に(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 静かにすれば、赤ちゃんが(   )。</t>
+          <t>: もんだい3 静かにすれば、赤ちゃんが(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1110,12 +1110,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 運動すれば、健康が(   )。</t>
+          <t>: もんだい3 運動すれば、健康が(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1134,12 +1134,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 早く寝れば、朝早く(   )。</t>
+          <t>: もんだい3 早く寝れば、朝早く(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1158,22 +1158,22 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降れば、 ピクニックは (   ).</t>
+          <t>: もんだい4 もし雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. 中止したい 2. 中止する 3. 中止しよう 4. 中止した</t>
+          <t>1. 中止にします 2. 中止になります 3. 中止したいです 4. 中止しました</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr"/>
@@ -1182,12 +1182,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼が 来れば、 映画を 一緒に (   ).</t>
+          <t>: もんだい4 彼が 来れば、 映画を 一緒に (   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1206,12 +1206,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 この薬を 飲めば、 すぐに (   ).</t>
+          <t>: もんだい4 この薬を 飲めば、 すぐに (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1230,12 +1230,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格すれば、 大学に (   ).</t>
+          <t>: もんだい4 もし 試験に 合格すれば、 大学に (   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1254,22 +1254,22 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 時間が あれば、 あなたに 手紙を (   ).</t>
+          <t>: もんだい4 時間があれば、あなたに手紙を(   )。</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1. 書く 2. 書くことにした 3. 書きたい 4. 書こうと思う</t>
+          <t>1. 書きます 2. 書くことにしました 3. 書きたいです 4. 書こうと思います</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が 来れば、 一緒に (   ).</t>
+          <t>: もんだい4 もし 彼女が 来れば、 一緒に (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1302,12 +1302,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼女が 手伝えば、 もっと 早く (   ).</t>
+          <t>: もんだい4 彼女が 手伝えば、 もっと 早く (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1326,17 +1326,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が あれば、 新しいスマホを (   ).</t>
+          <t>: もんだい4 もしお金があれば、新しいスマホを(   )。</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買う 3. 買おう 4. 買うことにした</t>
+          <t>1. 買います 2. 買いたいです 3. 買おうと思います 4. 買うことにしました</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1350,12 +1350,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もっと 練習すれば、 試合に (   )。</t>
+          <t>: もんだい4 もっと 練習すれば、 試合に (   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1374,12 +1374,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 これを やれば、 すぐに 終わると (   ).</t>
+          <t>: もんだい4 これを やれば、 すぐに 終わると (   ).</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この本は面白いが、あの本 (   ) 面白くない。</t>
+          <t>: もんだい5 この本は面白いが、あの本は(   )面白くない。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1422,12 +1422,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この道をまっすぐ行け (   ) 駅に着きますよ。</t>
+          <t>: もんだい5 この道をまっすぐ行け (   ) 駅に着きますよ。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降らなけれ (   ) ピクニックに行きます。</t>
+          <t>: もんだい5 雨が降らなけれ (   ) ピクニックに行きます。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1470,12 +1470,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 宿題を終わらせれ (   ) 遊びに行ってもいいです。</t>
+          <t>: もんだい5 宿題を終わらせれ (   ) 遊びに行ってもいいです。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1494,12 +1494,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この映画は怖いが、あの映画 (   ) 怖くない。</t>
+          <t>: もんだい5 この映画は怖いが、あの映画 (   ) 怖くない。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 たくさん練習すれ (   ) 上手になります。</t>
+          <t>: もんだい5 たくさん練習すれ (   ) 上手になります。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1542,12 +1542,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 お金があれ (   ) 旅行に行きたいです。</t>
+          <t>: もんだい5 お金があれ (   ) 旅行に行きたいです。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1566,12 +1566,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 早く寝れ (   ) 明日元気になります。</t>
+          <t>: もんだい5 早く寝れ (   ) 明日元気になります。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1590,12 +1590,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼は賢いが、彼女 (   ) 賢くない。</t>
+          <t>: もんだい5 彼は賢いが、彼女 (   ) 賢くない。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 勉強すれ (   ) するほど、試験が簡単になります。</t>
+          <t>: もんだい5 勉強すれ (   ) するほど、試験が簡単になります。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨が降れば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「雨が降れば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この本、面白ければ、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「この本、面白ければ、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1686,12 +1686,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「時間があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「時間があれば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1710,12 +1710,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「いい天気なら、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「いい天気なら、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし暇があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「もし暇があれば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1758,12 +1758,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「風邪を引いたら、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「風邪を引いたら、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1782,12 +1782,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「道が分からなければ、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「道が分からなければ、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1806,12 +1806,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「お金があれば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「お金があれば、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1830,12 +1830,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「疲れたら、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「疲れたら、」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1854,12 +1854,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「彼が来れば、」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「彼が来れば、」 B:「(   )。」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
@@ -1878,17 +1878,17 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 雨が降れば、ピクニックは(   )。</t>
+          <t>: もんだい7 雨が降れば、ピクニックは(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 中止にしよう 2. 中止になる 3. 中止にする 4. 中止できる</t>
+          <t>1. 中止にします 2. 中止になります 3. 中止したいです 4. 中止できます</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -1902,12 +1902,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 あの映画は面白ければ、(   )。</t>
+          <t>: もんだい7 あの映画は面白ければ、(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1926,12 +1926,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 勉強すれば、テストに(   )。</t>
+          <t>: もんだい7 勉強すれば、テストに(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 このボタンを押せば、(   )。</t>
+          <t>: もんだい7 このボタンを押せば、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1974,12 +1974,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 この薬を飲めば、(   )。</t>
+          <t>: もんだい7 この薬を飲めば、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -1998,12 +1998,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 時間があれば、(   )。</t>
+          <t>: もんだい7 時間があれば、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 家に帰れば、(   )。</t>
+          <t>: もんだい7 家に帰れば、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2046,12 +2046,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 お金があれば、(   )。</t>
+          <t>: もんだい7 お金があれば、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼が来れば、(   )。</t>
+          <t>: もんだい7 彼が来れば、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2094,12 +2094,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 この本を読めば、(   )。</t>
+          <t>: もんだい7 この本を読めば、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2118,12 +2118,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 雨が降れば、道が(   )なる。</t>
+          <t>: もんだい8 雨が降れば、道が(   )なる。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2142,17 +2142,17 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 その子供は、大人の(   )賢い。</t>
+          <t>: もんだい8 その子供は、大人のよう(   )賢い。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. らしく 4. みたい</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2166,22 +2166,22 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女が笑えば、太陽の(   )明るくなる。</t>
+          <t>: もんだい8 彼女が笑えば、太陽のよう(   )明るくなる。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr"/>
@@ -2190,22 +2190,22 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし疲れれば、猫の(   )眠ることができる。</t>
+          <t>: もんだい8 もし疲れれば、猫のよう(   )眠ることができる。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr"/>
@@ -2214,22 +2214,22 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼が来れば、すべてが(   )解決する。</t>
+          <t>: もんだい8 彼が来れば、すべてがまるで夢のよう(   )解決する。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>1. らしく 2. みたいに 3. ように 4. ほど</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr"/>
@@ -2238,22 +2238,22 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この歌を聴けば、昔の(   )思い出す。</t>
+          <t>: もんだい8 この歌を聴けば、昔のことがまるで映画のよう(   )思い出す。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr"/>
@@ -2262,17 +2262,17 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女が手伝えば、仕事が(   )早く終わる。</t>
+          <t>: もんだい8 彼女が手伝えば、仕事がまるで魔法のよう(   )早く終わる。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -2286,22 +2286,22 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 あの映画を見れば、夢の(   )感じる。</t>
+          <t>: もんだい8 あの映画を見れば、夢のよう(   )感じる。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. らしく 4. みたいに</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr"/>
@@ -2310,17 +2310,17 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼が説明すれば、子供でも(   )わかる。</t>
+          <t>: もんだい8 彼が説明すれば、子供でもわかるよう(   )になる。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -2334,22 +2334,22 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この薬を飲めば、魔法の(   )効く。</t>
+          <t>: もんだい8 この薬を飲めば、魔法のよう(   )効く。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+          <t>1. に 2. で 3. な 4. と</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr"/>
